--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/72.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/72.xlsx
@@ -426,13 +426,13 @@
         <v>-9.369017047719177</v>
       </c>
       <c r="E2">
-        <v>-9.379608393568837</v>
+        <v>-7.975473514958505</v>
       </c>
       <c r="F2">
-        <v>-6.021787989039415</v>
+        <v>-6.211132068134313</v>
       </c>
       <c r="G2">
-        <v>-10.01144840034264</v>
+        <v>-7.930571896178347</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.426795005004685</v>
       </c>
       <c r="E3">
-        <v>-10.42156497799371</v>
+        <v>-9.440208432739482</v>
       </c>
       <c r="F3">
-        <v>-5.975150075894401</v>
+        <v>-6.189558067495803</v>
       </c>
       <c r="G3">
-        <v>-8.987811166872298</v>
+        <v>-7.813944687375363</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.523742737275782</v>
       </c>
       <c r="E4">
-        <v>-10.34900976744282</v>
+        <v>-8.794792203270273</v>
       </c>
       <c r="F4">
-        <v>-6.300659531926675</v>
+        <v>-6.163093385711164</v>
       </c>
       <c r="G4">
-        <v>-9.457994707632826</v>
+        <v>-8.167405013512269</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.664862108461456</v>
       </c>
       <c r="E5">
-        <v>-12.8929162690437</v>
+        <v>-9.937059015439051</v>
       </c>
       <c r="F5">
-        <v>-5.567632246984975</v>
+        <v>-6.209876263151669</v>
       </c>
       <c r="G5">
-        <v>-9.51725347278578</v>
+        <v>-7.963670730479981</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.838103492072584</v>
       </c>
       <c r="E6">
-        <v>-12.42945412520269</v>
+        <v>-11.18503399636888</v>
       </c>
       <c r="F6">
-        <v>-5.982458761489301</v>
+        <v>-5.962250738698007</v>
       </c>
       <c r="G6">
-        <v>-9.776823416883417</v>
+        <v>-8.120534309767267</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.03299060922835</v>
       </c>
       <c r="E7">
-        <v>-14.17170298712172</v>
+        <v>-12.10171940431957</v>
       </c>
       <c r="F7">
-        <v>-5.630412555708345</v>
+        <v>-5.748937848803107</v>
       </c>
       <c r="G7">
-        <v>-8.874818937071433</v>
+        <v>-7.692460908266267</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.22971585898149</v>
       </c>
       <c r="E8">
-        <v>-13.65585545595997</v>
+        <v>-12.97171624525117</v>
       </c>
       <c r="F8">
-        <v>-5.285674207154885</v>
+        <v>-5.88451342814969</v>
       </c>
       <c r="G8">
-        <v>-9.130495679614885</v>
+        <v>-7.619503105671809</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.40003399204979</v>
       </c>
       <c r="E9">
-        <v>-14.9403752221317</v>
+        <v>-13.52103825627762</v>
       </c>
       <c r="F9">
-        <v>-5.68530017981784</v>
+        <v>-5.631293938624923</v>
       </c>
       <c r="G9">
-        <v>-10.05638243494717</v>
+        <v>-7.533501753652622</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.52563941718909</v>
       </c>
       <c r="E10">
-        <v>-16.86283470718597</v>
+        <v>-13.99760127542282</v>
       </c>
       <c r="F10">
-        <v>-5.394542393067811</v>
+        <v>-5.561108025320527</v>
       </c>
       <c r="G10">
-        <v>-8.889103941073389</v>
+        <v>-7.17070899964051</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.57472314788305</v>
       </c>
       <c r="E11">
-        <v>-16.54828237413918</v>
+        <v>-15.12006959923007</v>
       </c>
       <c r="F11">
-        <v>-5.165177399641461</v>
+        <v>-5.58667724194274</v>
       </c>
       <c r="G11">
-        <v>-9.103044636003249</v>
+        <v>-7.019069461214194</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.54478578544944</v>
       </c>
       <c r="E12">
-        <v>-16.86935118128301</v>
+        <v>-15.83455411426426</v>
       </c>
       <c r="F12">
-        <v>-4.979764752240251</v>
+        <v>-5.469296752598646</v>
       </c>
       <c r="G12">
-        <v>-9.147730379692332</v>
+        <v>-6.508047030681214</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.41854738687486</v>
       </c>
       <c r="E13">
-        <v>-17.7574030480832</v>
+        <v>-16.93073917493099</v>
       </c>
       <c r="F13">
-        <v>-4.999016010681311</v>
+        <v>-5.413437453525668</v>
       </c>
       <c r="G13">
-        <v>-9.415325086177161</v>
+        <v>-6.522984212154406</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.21034583666671</v>
       </c>
       <c r="E14">
-        <v>-18.11871640373319</v>
+        <v>-17.62053444967537</v>
       </c>
       <c r="F14">
-        <v>-4.175820933944886</v>
+        <v>-4.901245462863691</v>
       </c>
       <c r="G14">
-        <v>-8.757102558786027</v>
+        <v>-5.800335158023517</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.923565380498605</v>
       </c>
       <c r="E15">
-        <v>-20.22187105864153</v>
+        <v>-18.36338985436762</v>
       </c>
       <c r="F15">
-        <v>-4.709173569911375</v>
+        <v>-4.776866097333345</v>
       </c>
       <c r="G15">
-        <v>-8.506967669475314</v>
+        <v>-5.351276208349077</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.578902419841729</v>
       </c>
       <c r="E16">
-        <v>-20.00566812409332</v>
+        <v>-19.76228981702509</v>
       </c>
       <c r="F16">
-        <v>-3.851020560409408</v>
+        <v>-4.444286525518177</v>
       </c>
       <c r="G16">
-        <v>-7.132333155749279</v>
+        <v>-5.088365923802316</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.196402405543427</v>
       </c>
       <c r="E17">
-        <v>-20.6190091721662</v>
+        <v>-20.23945059473931</v>
       </c>
       <c r="F17">
-        <v>-4.238289776524802</v>
+        <v>-4.692419010822352</v>
       </c>
       <c r="G17">
-        <v>-6.917846220805438</v>
+        <v>-4.742159002941953</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.797011563564498</v>
       </c>
       <c r="E18">
-        <v>-22.50595183557832</v>
+        <v>-21.55893923719826</v>
       </c>
       <c r="F18">
-        <v>-3.523269542185158</v>
+        <v>-4.023280390188968</v>
       </c>
       <c r="G18">
-        <v>-7.212719822533862</v>
+        <v>-4.811342783621642</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.410467465277197</v>
       </c>
       <c r="E19">
-        <v>-22.79754480540622</v>
+        <v>-21.79320625456307</v>
       </c>
       <c r="F19">
-        <v>-3.555375405982861</v>
+        <v>-3.995458842598544</v>
       </c>
       <c r="G19">
-        <v>-6.694295012175073</v>
+        <v>-4.602513571004416</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.049113832230626</v>
       </c>
       <c r="E20">
-        <v>-23.83794812324646</v>
+        <v>-23.264996534848</v>
       </c>
       <c r="F20">
-        <v>-2.854000867869534</v>
+        <v>-3.651685542069346</v>
       </c>
       <c r="G20">
-        <v>-6.452648361627051</v>
+        <v>-4.52327566352196</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.741427915640956</v>
       </c>
       <c r="E21">
-        <v>-24.42519157561314</v>
+        <v>-24.10803537001194</v>
       </c>
       <c r="F21">
-        <v>-2.497875780997193</v>
+        <v>-3.135199294791257</v>
       </c>
       <c r="G21">
-        <v>-6.131032173032394</v>
+        <v>-4.182342441705656</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.48589190380005</v>
       </c>
       <c r="E22">
-        <v>-24.97781937266518</v>
+        <v>-25.10790431700952</v>
       </c>
       <c r="F22">
-        <v>-2.409870856491176</v>
+        <v>-2.97219315726837</v>
       </c>
       <c r="G22">
-        <v>-7.473527910663186</v>
+        <v>-4.477010789610645</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.297526571585699</v>
       </c>
       <c r="E23">
-        <v>-25.32339175266452</v>
+        <v>-25.95288586752276</v>
       </c>
       <c r="F23">
-        <v>-2.481915626247455</v>
+        <v>-2.920207304170882</v>
       </c>
       <c r="G23">
-        <v>-5.859388669353036</v>
+        <v>-4.366054545316432</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.164603685604079</v>
       </c>
       <c r="E24">
-        <v>-26.79495560924906</v>
+        <v>-25.86515121209815</v>
       </c>
       <c r="F24">
-        <v>-2.202556174959947</v>
+        <v>-2.538762339264571</v>
       </c>
       <c r="G24">
-        <v>-6.507626591397727</v>
+        <v>-4.355457489045225</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.082270362078099</v>
       </c>
       <c r="E25">
-        <v>-25.81466778386064</v>
+        <v>-25.61386166093852</v>
       </c>
       <c r="F25">
-        <v>-2.071497683060829</v>
+        <v>-2.71025841429875</v>
       </c>
       <c r="G25">
-        <v>-6.507411405937675</v>
+        <v>-4.533955483431649</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.036093010654283</v>
       </c>
       <c r="E26">
-        <v>-26.84254081412166</v>
+        <v>-25.67877733583847</v>
       </c>
       <c r="F26">
-        <v>-1.570409129065977</v>
+        <v>-2.432423159032393</v>
       </c>
       <c r="G26">
-        <v>-6.713314096298186</v>
+        <v>-4.722517536257457</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.010515059419373</v>
       </c>
       <c r="E27">
-        <v>-26.80933351422341</v>
+        <v>-26.99256010104776</v>
       </c>
       <c r="F27">
-        <v>-2.00781776733802</v>
+        <v>-2.350476913710452</v>
       </c>
       <c r="G27">
-        <v>-7.472713516460525</v>
+        <v>-4.670588318928449</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.996048111681771</v>
       </c>
       <c r="E28">
-        <v>-26.47607405505094</v>
+        <v>-26.82139736897985</v>
       </c>
       <c r="F28">
-        <v>-2.012660403174785</v>
+        <v>-2.704703382495576</v>
       </c>
       <c r="G28">
-        <v>-7.295831068297265</v>
+        <v>-4.714525879325657</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.972164389400724</v>
       </c>
       <c r="E29">
-        <v>-26.84289403509426</v>
+        <v>-25.77922794627662</v>
       </c>
       <c r="F29">
-        <v>-2.078730158854671</v>
+        <v>-2.533841008524539</v>
       </c>
       <c r="G29">
-        <v>-7.172155708041172</v>
+        <v>-4.941000299667198</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.934861456225738</v>
       </c>
       <c r="E30">
-        <v>-26.65562352098106</v>
+        <v>-26.22837558377939</v>
       </c>
       <c r="F30">
-        <v>-2.167496353003861</v>
+        <v>-2.686482613103598</v>
       </c>
       <c r="G30">
-        <v>-6.685988853417041</v>
+        <v>-5.611465224462556</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.863955300739664</v>
       </c>
       <c r="E31">
-        <v>-25.85788753978985</v>
+        <v>-26.1227625129725</v>
       </c>
       <c r="F31">
-        <v>-2.129591089019158</v>
+        <v>-3.107317276380428</v>
       </c>
       <c r="G31">
-        <v>-7.169682730523337</v>
+        <v>-5.400371598696468</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.761064155137157</v>
       </c>
       <c r="E32">
-        <v>-25.35543070626878</v>
+        <v>-25.26952555434328</v>
       </c>
       <c r="F32">
-        <v>-2.135185882457666</v>
+        <v>-2.774432036993628</v>
       </c>
       <c r="G32">
-        <v>-6.90161792657193</v>
+        <v>-5.283737768802405</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.616982914583355</v>
       </c>
       <c r="E33">
-        <v>-25.45494392258734</v>
+        <v>-25.06143764521682</v>
       </c>
       <c r="F33">
-        <v>-2.196993687850148</v>
+        <v>-2.694710786515606</v>
       </c>
       <c r="G33">
-        <v>-6.877480739045104</v>
+        <v>-4.922073910819185</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.437458974491869</v>
       </c>
       <c r="E34">
-        <v>-23.63766730330923</v>
+        <v>-25.05901944009672</v>
       </c>
       <c r="F34">
-        <v>-2.162376214087157</v>
+        <v>-2.615251300136869</v>
       </c>
       <c r="G34">
-        <v>-6.811663783178854</v>
+        <v>-5.088111011795792</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.227495862911582</v>
       </c>
       <c r="E35">
-        <v>-24.03981390908638</v>
+        <v>-24.54716602300974</v>
       </c>
       <c r="F35">
-        <v>-2.444452710455847</v>
+        <v>-2.796341526430272</v>
       </c>
       <c r="G35">
-        <v>-7.61800342854252</v>
+        <v>-4.860050840140939</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.995734861818038</v>
       </c>
       <c r="E36">
-        <v>-24.10903163429363</v>
+        <v>-23.83303925742215</v>
       </c>
       <c r="F36">
-        <v>-2.022152665243465</v>
+        <v>-2.709624713235608</v>
       </c>
       <c r="G36">
-        <v>-6.54586339237631</v>
+        <v>-4.937388494483853</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.757884214969658</v>
       </c>
       <c r="E37">
-        <v>-24.72525732030939</v>
+        <v>-23.0690494645361</v>
       </c>
       <c r="F37">
-        <v>-2.333318939696265</v>
+        <v>-2.71729788048774</v>
       </c>
       <c r="G37">
-        <v>-6.285849835176411</v>
+        <v>-3.951653696892622</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.523378137342522</v>
       </c>
       <c r="E38">
-        <v>-22.69218080066976</v>
+        <v>-22.73873351346861</v>
       </c>
       <c r="F38">
-        <v>-2.080758002256724</v>
+        <v>-2.689513609430442</v>
       </c>
       <c r="G38">
-        <v>-6.242405546064555</v>
+        <v>-3.714175023178543</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.314088187177038</v>
       </c>
       <c r="E39">
-        <v>-22.14159987386918</v>
+        <v>-22.72843123510116</v>
       </c>
       <c r="F39">
-        <v>-2.183454851018793</v>
+        <v>-2.948357713620217</v>
       </c>
       <c r="G39">
-        <v>-5.685316874352618</v>
+        <v>-3.635092711336433</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.133090173824704</v>
       </c>
       <c r="E40">
-        <v>-23.69666879115517</v>
+        <v>-22.17529624896025</v>
       </c>
       <c r="F40">
-        <v>-2.638199562296624</v>
+        <v>-2.907451274535172</v>
       </c>
       <c r="G40">
-        <v>-5.688137459152077</v>
+        <v>-3.396839369966164</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.993998746292312</v>
       </c>
       <c r="E41">
-        <v>-22.90161366657649</v>
+        <v>-21.91533467007593</v>
       </c>
       <c r="F41">
-        <v>-2.430900619746047</v>
+        <v>-2.697817164276104</v>
       </c>
       <c r="G41">
-        <v>-5.429262729617688</v>
+        <v>-2.799150167760605</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.891435830361656</v>
       </c>
       <c r="E42">
-        <v>-20.73833446226832</v>
+        <v>-20.67856313384108</v>
       </c>
       <c r="F42">
-        <v>-2.175333537001747</v>
+        <v>-2.851533161376594</v>
       </c>
       <c r="G42">
-        <v>-5.272121064505103</v>
+        <v>-2.832702546801118</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.825804971976407</v>
       </c>
       <c r="E43">
-        <v>-20.8025572806451</v>
+        <v>-20.78713329817498</v>
       </c>
       <c r="F43">
-        <v>-2.693675327262107</v>
+        <v>-2.731489470832501</v>
       </c>
       <c r="G43">
-        <v>-5.253065564381058</v>
+        <v>-2.616977467825589</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.788789823442912</v>
       </c>
       <c r="E44">
-        <v>-20.72713101757334</v>
+        <v>-20.35638485056537</v>
       </c>
       <c r="F44">
-        <v>-1.987126806350893</v>
+        <v>-2.694189743419245</v>
       </c>
       <c r="G44">
-        <v>-4.906150186775291</v>
+        <v>-2.345883514705751</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.773027758163516</v>
       </c>
       <c r="E45">
-        <v>-19.83800137395933</v>
+        <v>-19.74336532414703</v>
       </c>
       <c r="F45">
-        <v>-2.816576885345858</v>
+        <v>-2.681560453996164</v>
       </c>
       <c r="G45">
-        <v>-5.045563880525079</v>
+        <v>-2.701270578346513</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.77494914958192</v>
       </c>
       <c r="E46">
-        <v>-20.21347979630531</v>
+        <v>-18.47130791844441</v>
       </c>
       <c r="F46">
-        <v>-2.494365988311531</v>
+        <v>-2.721292268104039</v>
       </c>
       <c r="G46">
-        <v>-5.531350022412194</v>
+        <v>-2.4240587370701</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.783808975149817</v>
       </c>
       <c r="E47">
-        <v>-18.40401479469043</v>
+        <v>-18.70262237075622</v>
       </c>
       <c r="F47">
-        <v>-2.878164345009196</v>
+        <v>-2.938225123549174</v>
       </c>
       <c r="G47">
-        <v>-5.316310226363294</v>
+        <v>-2.11949516854823</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.80267156740596</v>
       </c>
       <c r="E48">
-        <v>-17.41265485035326</v>
+        <v>-17.79233116810436</v>
       </c>
       <c r="F48">
-        <v>-2.735130973935208</v>
+        <v>-3.212702177364581</v>
       </c>
       <c r="G48">
-        <v>-4.699006041837553</v>
+        <v>-1.597978308655761</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.823161788131938</v>
       </c>
       <c r="E49">
-        <v>-17.54434740297032</v>
+        <v>-17.43809128885434</v>
       </c>
       <c r="F49">
-        <v>-3.187513181380254</v>
+        <v>-3.111628100344597</v>
       </c>
       <c r="G49">
-        <v>-4.10115131235503</v>
+        <v>-2.15932765247674</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.856677600611849</v>
       </c>
       <c r="E50">
-        <v>-16.96885534065355</v>
+        <v>-16.6867948086118</v>
       </c>
       <c r="F50">
-        <v>-3.142513778957976</v>
+        <v>-3.157479064456953</v>
       </c>
       <c r="G50">
-        <v>-4.586212444769044</v>
+        <v>-2.17159653424528</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.90331954595066</v>
       </c>
       <c r="E51">
-        <v>-16.81570687818815</v>
+        <v>-16.7527429755855</v>
       </c>
       <c r="F51">
-        <v>-3.266808651013237</v>
+        <v>-3.307508826614985</v>
       </c>
       <c r="G51">
-        <v>-4.764015224592222</v>
+        <v>-1.994290336252993</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.976334312691546</v>
       </c>
       <c r="E52">
-        <v>-15.79690438136449</v>
+        <v>-15.70909274188176</v>
       </c>
       <c r="F52">
-        <v>-3.511714645283508</v>
+        <v>-3.408829757121004</v>
       </c>
       <c r="G52">
-        <v>-5.211796303688503</v>
+        <v>-2.171884551707196</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.081906481851934</v>
       </c>
       <c r="E53">
-        <v>-15.88878711898012</v>
+        <v>-14.79832152098509</v>
       </c>
       <c r="F53">
-        <v>-2.937098543881366</v>
+        <v>-3.21857530225043</v>
       </c>
       <c r="G53">
-        <v>-5.478553442151897</v>
+        <v>-2.306802524614654</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.226829137714692</v>
       </c>
       <c r="E54">
-        <v>-15.43709900755905</v>
+        <v>-15.34863979629322</v>
       </c>
       <c r="F54">
-        <v>-3.171951471351263</v>
+        <v>-3.447190623177246</v>
       </c>
       <c r="G54">
-        <v>-4.133021934261594</v>
+        <v>-1.984851970920531</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.417365335970002</v>
       </c>
       <c r="E55">
-        <v>-14.86842229862383</v>
+        <v>-14.70350433221249</v>
       </c>
       <c r="F55">
-        <v>-3.502349123427457</v>
+        <v>-3.458887999272178</v>
       </c>
       <c r="G55">
-        <v>-4.775228042333733</v>
+        <v>-2.209939272681118</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.648365961654767</v>
       </c>
       <c r="E56">
-        <v>-14.76872794334496</v>
+        <v>-13.99465776731784</v>
       </c>
       <c r="F56">
-        <v>-3.221634463068969</v>
+        <v>-3.477845187285244</v>
       </c>
       <c r="G56">
-        <v>-5.227110887353171</v>
+        <v>-2.391602148603086</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.924864727853783</v>
       </c>
       <c r="E57">
-        <v>-14.05702391135147</v>
+        <v>-13.31300016036524</v>
       </c>
       <c r="F57">
-        <v>-3.562450491970172</v>
+        <v>-3.60191391503954</v>
       </c>
       <c r="G57">
-        <v>-4.039479159503947</v>
+        <v>-1.761572227024386</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.232251712732354</v>
       </c>
       <c r="E58">
-        <v>-13.68872764878165</v>
+        <v>-12.51655479426622</v>
       </c>
       <c r="F58">
-        <v>-3.326051830926652</v>
+        <v>-3.789296420124608</v>
       </c>
       <c r="G58">
-        <v>-5.198722959353921</v>
+        <v>-2.039538872683752</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.574355133298984</v>
       </c>
       <c r="E59">
-        <v>-12.8746755757408</v>
+        <v>-12.33563320071177</v>
       </c>
       <c r="F59">
-        <v>-3.679855832336349</v>
+        <v>-3.540010019028333</v>
       </c>
       <c r="G59">
-        <v>-4.988039841234703</v>
+        <v>-2.447858248951921</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.936075990662108</v>
       </c>
       <c r="E60">
-        <v>-12.75333511470528</v>
+        <v>-12.31437654371977</v>
       </c>
       <c r="F60">
-        <v>-3.545765515742984</v>
+        <v>-4.035753946540323</v>
       </c>
       <c r="G60">
-        <v>-3.849844489923415</v>
+        <v>-1.92171655694109</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.318322664476931</v>
       </c>
       <c r="E61">
-        <v>-13.38122162129079</v>
+        <v>-11.92825620745575</v>
       </c>
       <c r="F61">
-        <v>-3.974595581191635</v>
+        <v>-3.524594930029637</v>
       </c>
       <c r="G61">
-        <v>-4.765756571545878</v>
+        <v>-2.330449751401668</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.713467765274</v>
       </c>
       <c r="E62">
-        <v>-12.23245644892101</v>
+        <v>-11.75158685099451</v>
       </c>
       <c r="F62">
-        <v>-3.735614070586186</v>
+        <v>-3.837961348304273</v>
       </c>
       <c r="G62">
-        <v>-4.54762141541776</v>
+        <v>-2.447398083121962</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.12009744889912</v>
       </c>
       <c r="E63">
-        <v>-11.85429264148847</v>
+        <v>-12.00288093062815</v>
       </c>
       <c r="F63">
-        <v>-3.737512688673403</v>
+        <v>-3.671020465618089</v>
       </c>
       <c r="G63">
-        <v>-5.254631452421133</v>
+        <v>-3.095596278620182</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.539271906818811</v>
       </c>
       <c r="E64">
-        <v>-12.89700095259862</v>
+        <v>-10.85489465578769</v>
       </c>
       <c r="F64">
-        <v>-3.856733810386516</v>
+        <v>-3.969328821244636</v>
       </c>
       <c r="G64">
-        <v>-6.009439145920503</v>
+        <v>-2.789533032969021</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.962820483844977</v>
       </c>
       <c r="E65">
-        <v>-10.83198057730887</v>
+        <v>-11.08848240205134</v>
       </c>
       <c r="F65">
-        <v>-3.825534180527475</v>
+        <v>-3.72122864226917</v>
       </c>
       <c r="G65">
-        <v>-5.515681210374823</v>
+        <v>-2.846679670067921</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.395622522957428</v>
       </c>
       <c r="E66">
-        <v>-11.69976299445073</v>
+        <v>-10.22234834944827</v>
       </c>
       <c r="F66">
-        <v>-4.04299056417118</v>
+        <v>-3.762655296083173</v>
       </c>
       <c r="G66">
-        <v>-6.014971067516625</v>
+        <v>-3.518763451631982</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.819548606477619</v>
       </c>
       <c r="E67">
-        <v>-11.88402207334883</v>
+        <v>-10.02205847256302</v>
       </c>
       <c r="F67">
-        <v>-3.88443690143834</v>
+        <v>-3.787285144070611</v>
       </c>
       <c r="G67">
-        <v>-5.415106836891765</v>
+        <v>-3.291415047268073</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.23664754258466</v>
       </c>
       <c r="E68">
-        <v>-11.68973695299775</v>
+        <v>-10.17919199215518</v>
       </c>
       <c r="F68">
-        <v>-3.895047459500799</v>
+        <v>-3.912610505174954</v>
       </c>
       <c r="G68">
-        <v>-4.853889914892355</v>
+        <v>-2.843200286706147</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.62401351795888</v>
       </c>
       <c r="E69">
-        <v>-10.80151300418527</v>
+        <v>-9.75177197294121</v>
       </c>
       <c r="F69">
-        <v>-4.179399481124979</v>
+        <v>-3.90968305477346</v>
       </c>
       <c r="G69">
-        <v>-6.56593854052645</v>
+        <v>-3.301790296988149</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.97539630273659</v>
       </c>
       <c r="E70">
-        <v>-11.46515634153535</v>
+        <v>-9.414504814271945</v>
       </c>
       <c r="F70">
-        <v>-3.859783030796221</v>
+        <v>-4.010970022215965</v>
       </c>
       <c r="G70">
-        <v>-6.125059948879549</v>
+        <v>-3.42801477730948</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.27214892996733</v>
       </c>
       <c r="E71">
-        <v>-10.75787662864736</v>
+        <v>-9.969664028294277</v>
       </c>
       <c r="F71">
-        <v>-4.47192417554518</v>
+        <v>-4.092714974259025</v>
       </c>
       <c r="G71">
-        <v>-6.040356330711757</v>
+        <v>-3.496884056162939</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.50311919497428</v>
       </c>
       <c r="E72">
-        <v>-11.83787239473666</v>
+        <v>-10.7538281728845</v>
       </c>
       <c r="F72">
-        <v>-4.150247575485659</v>
+        <v>-4.140809985665564</v>
       </c>
       <c r="G72">
-        <v>-5.04478590232335</v>
+        <v>-3.484605242757782</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.66001152597303</v>
       </c>
       <c r="E73">
-        <v>-11.62352160605759</v>
+        <v>-10.23350198092917</v>
       </c>
       <c r="F73">
-        <v>-4.195761394065075</v>
+        <v>-4.318170901911563</v>
       </c>
       <c r="G73">
-        <v>-5.483519260460803</v>
+        <v>-3.107971097845978</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.7296219692596</v>
       </c>
       <c r="E74">
-        <v>-12.01156654377487</v>
+        <v>-10.26499298917851</v>
       </c>
       <c r="F74">
-        <v>-4.430094106806013</v>
+        <v>-4.16027579126395</v>
       </c>
       <c r="G74">
-        <v>-4.632000600122704</v>
+        <v>-3.091123731596627</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.71583302867865</v>
       </c>
       <c r="E75">
-        <v>-10.78631091694152</v>
+        <v>-10.06065012805639</v>
       </c>
       <c r="F75">
-        <v>-4.397714053397983</v>
+        <v>-4.418663465014783</v>
       </c>
       <c r="G75">
-        <v>-5.119120891862146</v>
+        <v>-2.704693682434119</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.60622581679028</v>
       </c>
       <c r="E76">
-        <v>-12.52966925499243</v>
+        <v>-11.24072516971521</v>
       </c>
       <c r="F76">
-        <v>-4.527535792764722</v>
+        <v>-4.474754706960546</v>
       </c>
       <c r="G76">
-        <v>-5.164276733017805</v>
+        <v>-2.336200169003382</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.41625691502891</v>
       </c>
       <c r="E77">
-        <v>-12.4861415628307</v>
+        <v>-10.84394480563714</v>
       </c>
       <c r="F77">
-        <v>-4.647297838391864</v>
+        <v>-4.606809724845232</v>
       </c>
       <c r="G77">
-        <v>-5.420105760656064</v>
+        <v>-2.487462305238222</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.14325942509062</v>
       </c>
       <c r="E78">
-        <v>-12.9271560610157</v>
+        <v>-11.17201463359683</v>
       </c>
       <c r="F78">
-        <v>-4.805590565392821</v>
+        <v>-4.73191474022043</v>
       </c>
       <c r="G78">
-        <v>-4.756013636023803</v>
+        <v>-2.287319964116043</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.80856644768167</v>
       </c>
       <c r="E79">
-        <v>-13.95672726902959</v>
+        <v>-12.01490402911852</v>
       </c>
       <c r="F79">
-        <v>-4.71374947144444</v>
+        <v>-4.728071943838843</v>
       </c>
       <c r="G79">
-        <v>-4.356735359623384</v>
+        <v>-1.907997656226351</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.42278160662713</v>
       </c>
       <c r="E80">
-        <v>-15.29160366616661</v>
+        <v>-11.9955900874758</v>
       </c>
       <c r="F80">
-        <v>-4.794635406490797</v>
+        <v>-5.035737537647413</v>
       </c>
       <c r="G80">
-        <v>-3.643723303557313</v>
+        <v>-1.934038407438258</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.005449007619</v>
       </c>
       <c r="E81">
-        <v>-14.11943986859919</v>
+        <v>-13.10033849249103</v>
       </c>
       <c r="F81">
-        <v>-4.948345605019468</v>
+        <v>-4.711565066603257</v>
       </c>
       <c r="G81">
-        <v>-3.640806712937215</v>
+        <v>-1.571626366163162</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.577264660794036</v>
       </c>
       <c r="E82">
-        <v>-14.96315344639028</v>
+        <v>-13.72049036547145</v>
       </c>
       <c r="F82">
-        <v>-4.889756006986862</v>
+        <v>-5.155802765743979</v>
       </c>
       <c r="G82">
-        <v>-4.002156069094204</v>
+        <v>-1.673902360053406</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.15158544260019</v>
       </c>
       <c r="E83">
-        <v>-16.11804111561844</v>
+        <v>-14.87074993426377</v>
       </c>
       <c r="F83">
-        <v>-5.198304640446816</v>
+        <v>-5.554724626114554</v>
       </c>
       <c r="G83">
-        <v>-4.297532873744597</v>
+        <v>-1.144781177057232</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.754353278258426</v>
       </c>
       <c r="E84">
-        <v>-16.82094179414101</v>
+        <v>-15.18677854983706</v>
       </c>
       <c r="F84">
-        <v>-4.93839525577704</v>
+        <v>-5.414993127508125</v>
       </c>
       <c r="G84">
-        <v>-3.691100520769822</v>
+        <v>-1.638340479870555</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.387688994892821</v>
       </c>
       <c r="E85">
-        <v>-17.34857241467072</v>
+        <v>-16.03610743539766</v>
       </c>
       <c r="F85">
-        <v>-5.242256158104552</v>
+        <v>-5.980614815650669</v>
       </c>
       <c r="G85">
-        <v>-3.173711911164825</v>
+        <v>-1.495977090045276</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.074690282115304</v>
       </c>
       <c r="E86">
-        <v>-19.06694716162131</v>
+        <v>-17.05807080707866</v>
       </c>
       <c r="F86">
-        <v>-5.738275931961674</v>
+        <v>-5.482709677584776</v>
       </c>
       <c r="G86">
-        <v>-3.42533654596821</v>
+        <v>-0.899641900965279</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.808178065498004</v>
       </c>
       <c r="E87">
-        <v>-20.58193908393941</v>
+        <v>-18.72319522817306</v>
       </c>
       <c r="F87">
-        <v>-5.930660119424845</v>
+        <v>-5.758666195581584</v>
       </c>
       <c r="G87">
-        <v>-2.943039719079487</v>
+        <v>-0.6727933889777994</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.59999982552482</v>
       </c>
       <c r="E88">
-        <v>-21.01928098970419</v>
+        <v>-19.88699040577431</v>
       </c>
       <c r="F88">
-        <v>-5.941665808738439</v>
+        <v>-5.748082145276014</v>
       </c>
       <c r="G88">
-        <v>-2.89928423868694</v>
+        <v>-0.6164114878984719</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.442689612748002</v>
       </c>
       <c r="E89">
-        <v>-22.8827842716526</v>
+        <v>-20.7984273123501</v>
       </c>
       <c r="F89">
-        <v>-6.206672966405043</v>
+        <v>-5.877473133593297</v>
       </c>
       <c r="G89">
-        <v>-2.538252694901721</v>
+        <v>-0.6097341175457619</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.336299977330637</v>
       </c>
       <c r="E90">
-        <v>-24.3073289826155</v>
+        <v>-22.20492605439244</v>
       </c>
       <c r="F90">
-        <v>-5.985851754371168</v>
+        <v>-6.05674675017236</v>
       </c>
       <c r="G90">
-        <v>-4.141953786126548</v>
+        <v>-1.235172312461492</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.278782704455877</v>
       </c>
       <c r="E91">
-        <v>-24.80939636737191</v>
+        <v>-25.02860620866121</v>
       </c>
       <c r="F91">
-        <v>-6.01133233568128</v>
+        <v>-5.949821914186403</v>
       </c>
       <c r="G91">
-        <v>-2.541318260071086</v>
+        <v>-1.662586915400178</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.261815532241123</v>
       </c>
       <c r="E92">
-        <v>-27.86771487387411</v>
+        <v>-26.24737706071557</v>
       </c>
       <c r="F92">
-        <v>-6.307686986788324</v>
+        <v>-6.496582504934605</v>
       </c>
       <c r="G92">
-        <v>-4.439078558821676</v>
+        <v>-1.162492595692333</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.288951130901792</v>
       </c>
       <c r="E93">
-        <v>-30.0696174329937</v>
+        <v>-28.07135129305103</v>
       </c>
       <c r="F93">
-        <v>-6.229690811426633</v>
+        <v>-6.269122342350993</v>
       </c>
       <c r="G93">
-        <v>-3.653601971446498</v>
+        <v>-1.280420848892251</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.3449178402314</v>
       </c>
       <c r="E94">
-        <v>-31.47706715457765</v>
+        <v>-30.31087414998935</v>
       </c>
       <c r="F94">
-        <v>-6.660962075611334</v>
+        <v>-6.173511762536173</v>
       </c>
       <c r="G94">
-        <v>-3.490276207266554</v>
+        <v>-1.706925051807636</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.437482420364294</v>
       </c>
       <c r="E95">
-        <v>-34.26984726645508</v>
+        <v>-32.56760973663082</v>
       </c>
       <c r="F95">
-        <v>-6.468576231413357</v>
+        <v>-6.364046205588894</v>
       </c>
       <c r="G95">
-        <v>-5.408161312350374</v>
+        <v>-2.156010485846391</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.550501031596268</v>
       </c>
       <c r="E96">
-        <v>-36.15317167913506</v>
+        <v>-35.05323930622699</v>
       </c>
       <c r="F96">
-        <v>-6.491617270722226</v>
+        <v>-6.278779449532831</v>
       </c>
       <c r="G96">
-        <v>-4.502412605533473</v>
+        <v>-2.741540054286207</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.686142189707082</v>
       </c>
       <c r="E97">
-        <v>-37.15229116368438</v>
+        <v>-37.96634776519924</v>
       </c>
       <c r="F97">
-        <v>-6.670204999091771</v>
+        <v>-6.329319387328733</v>
       </c>
       <c r="G97">
-        <v>-5.372606053258601</v>
+        <v>-3.052387038241615</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.831483976250089</v>
       </c>
       <c r="E98">
-        <v>-40.10496942853565</v>
+        <v>-39.65774865672314</v>
       </c>
       <c r="F98">
-        <v>-7.220867200307159</v>
+        <v>-6.332579013058749</v>
       </c>
       <c r="G98">
-        <v>-5.404933530449584</v>
+        <v>-3.618218860722767</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.979085861442109</v>
       </c>
       <c r="E99">
-        <v>-42.96163045900227</v>
+        <v>-42.3843632348745</v>
       </c>
       <c r="F99">
-        <v>-7.121690084639585</v>
+        <v>-6.40249736369204</v>
       </c>
       <c r="G99">
-        <v>-5.385311927038324</v>
+        <v>-4.352322402419535</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.120014443261644</v>
       </c>
       <c r="E100">
-        <v>-44.34555702235338</v>
+        <v>-45.19093934281629</v>
       </c>
       <c r="F100">
-        <v>-7.246144003236183</v>
+        <v>-6.616876776618046</v>
       </c>
       <c r="G100">
-        <v>-6.598388507902386</v>
+        <v>-4.505173600513225</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.234088232776333</v>
       </c>
       <c r="E101">
-        <v>-47.54191473779439</v>
+        <v>-47.06165648385893</v>
       </c>
       <c r="F101">
-        <v>-7.328616261858902</v>
+        <v>-6.624961228285668</v>
       </c>
       <c r="G101">
-        <v>-6.673124073451433</v>
+        <v>-5.024684269808896</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.320402998539288</v>
       </c>
       <c r="E102">
-        <v>-50.18889610052086</v>
+        <v>-49.48277228062332</v>
       </c>
       <c r="F102">
-        <v>-6.943571626403726</v>
+        <v>-6.336155075136634</v>
       </c>
       <c r="G102">
-        <v>-7.540397620010924</v>
+        <v>-5.820642044361406</v>
       </c>
     </row>
   </sheetData>
